--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484536_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484536_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0739</v>
+        <v>2.7893</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4947</v>
+        <v>1.0524</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5792</v>
+        <v>1.7369</v>
       </c>
       <c r="G2" t="n">
         <v>1.7933</v>
@@ -610,13 +610,13 @@
         <v>3.2986</v>
       </c>
       <c r="S2" t="n">
-        <v>3.0493</v>
+        <v>0.7647</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4435</v>
+        <v>0.0012</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6058</v>
+        <v>0.7635</v>
       </c>
       <c r="V2" t="n">
         <v>1.5141</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. CARPIO MAÑEZ</t>
+          <t>F. BLASCO MANZANO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3251</v>
+        <v>0.661</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3251</v>
+        <v>1.4536</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0.7927</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3251</v>
+        <v>-0.4975</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3251</v>
+        <v>-0.5169</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.0194</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3251</v>
+        <v>0.4292</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3251</v>
+        <v>1.0187</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0.5895</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0.9267</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-1.5356</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.6089</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0.9802</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0.5645</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0.4157</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. OLID SANGÜESA</t>
+          <t>R. MEDINA LERMA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3251</v>
+        <v>0.4983</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3251</v>
+        <v>-0.7945</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1.2928</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3251</v>
+        <v>0.3664</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3251</v>
+        <v>-0.2711</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.6375</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3251</v>
+        <v>1.6948</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3251</v>
+        <v>1.5697</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-1.3284</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-1.8409</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.5125</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.9321</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.2802</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.3555</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.6875</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3863</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. MEDINA LERMA</t>
+          <t>J. CARPIO MAÑEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2972</v>
+        <v>0.3251</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6983</v>
+        <v>0.3251</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9955000000000001</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3664</v>
+        <v>0.3251</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2711</v>
+        <v>0.3251</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6375</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6948</v>
+        <v>0.3251</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5697</v>
+        <v>0.3251</v>
       </c>
       <c r="L5" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3284</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8409</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5125</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9321</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4813</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2594</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2219</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6875</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3011</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3863</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. BLASCO MANZANO</t>
+          <t>D. OLID SANGÜESA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2868</v>
+        <v>0.3251</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3024</v>
+        <v>0.3251</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0156</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4975</v>
+        <v>0.3251</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5169</v>
+        <v>0.3251</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0194</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4292</v>
+        <v>0.3251</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0187</v>
+        <v>0.3251</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5895</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9267</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5356</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6089</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3544</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7157</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6387</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. OLID SANGUESA</t>
+          <t>J. CARPIO MANEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1222</v>
+        <v>-0.0674</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8729</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7508</v>
+        <v>0.6851</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1734</v>
+        <v>-0.9333</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0452</v>
+        <v>-1.241</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1282</v>
+        <v>0.3076</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5977</v>
+        <v>-0.4493</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0433</v>
+        <v>-0.5327</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.641</v>
+        <v>0.0833</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4243</v>
+        <v>-0.484</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0885</v>
+        <v>-0.7083</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5128</v>
+        <v>0.2243</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2509</v>
+        <v>0.1329</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2753</v>
+        <v>-0.3032</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0244</v>
+        <v>0.4361</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0644</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.0644</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CARPIO MANEZ</t>
+          <t>D. OLID SANGUESA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4331</v>
+        <v>-0.1003</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9448</v>
+        <v>-0.7768</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5117</v>
+        <v>0.6764</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9333</v>
+        <v>-0.1734</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.241</v>
+        <v>-0.0452</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3076</v>
+        <v>-0.1282</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4493</v>
+        <v>-0.5977</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5327</v>
+        <v>0.0433</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0833</v>
+        <v>-0.641</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.484</v>
+        <v>0.4243</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7083</v>
+        <v>-0.0885</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2243</v>
+        <v>0.5128</v>
       </c>
       <c r="P8" t="n">
-        <v>0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2328</v>
+        <v>-0.2291</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4955</v>
+        <v>-0.1791</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2627</v>
+        <v>-0.05</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.0644</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.0644</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6736</v>
+        <v>-0.3053</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7099</v>
+        <v>-1.3663</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0363</v>
+        <v>1.061</v>
       </c>
       <c r="G9" t="n">
         <v>1.1892</v>
@@ -1156,13 +1156,13 @@
         <v>1.0995</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4963</v>
+        <v>-0.128</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6606</v>
+        <v>-0.3171</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1643</v>
+        <v>0.1891</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6335</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0892</v>
+        <v>-0.8637</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2061</v>
+        <v>-0.0549</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.883</v>
+        <v>-0.8087</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6621</v>
@@ -1234,13 +1234,13 @@
         <v>0.1833</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6103</v>
+        <v>-0.3848</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2753</v>
+        <v>-0.1241</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3351</v>
+        <v>-0.2608</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9257</v>
+        <v>-2.8573</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.562</v>
+        <v>-2.3697</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3637</v>
+        <v>-0.4875</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7519</v>
@@ -1312,13 +1312,13 @@
         <v>0.3665</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.302</v>
+        <v>-0.2336</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3854</v>
+        <v>-0.1931</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0833</v>
+        <v>-0.0405</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3219</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1191</v>
+        <v>-3.7811</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4115</v>
+        <v>-4.123</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2924</v>
+        <v>0.3419</v>
       </c>
       <c r="G12" t="n">
         <v>-3.1526</v>
@@ -1390,13 +1390,13 @@
         <v>3.1154</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2686</v>
+        <v>-0.9306</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0105</v>
+        <v>-0.7221</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2581</v>
+        <v>-0.2085</v>
       </c>
       <c r="V12" t="n">
         <v>-0.0644</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.4474</v>
+        <v>-4.8266</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3099</v>
+        <v>-3.6395</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1375</v>
+        <v>-1.1871</v>
       </c>
       <c r="G13" t="n">
         <v>-5.6965</v>
@@ -1468,13 +1468,13 @@
         <v>1.6493</v>
       </c>
       <c r="S13" t="n">
-        <v>0.516</v>
+        <v>0.1369</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2361</v>
+        <v>-0.0935</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2799</v>
+        <v>0.2304</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.1096</v>
+        <v>-5.0109</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.2943</v>
+        <v>-5.0469</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1847</v>
+        <v>0.036</v>
       </c>
       <c r="G14" t="n">
         <v>-3.6631</v>
@@ -1546,13 +1546,13 @@
         <v>0.9163</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8314</v>
+        <v>-0.7327</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.046</v>
+        <v>-0.7986</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2146</v>
+        <v>0.066</v>
       </c>
       <c r="V14" t="n">
         <v>0.3011</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-8.483700000000001</v>
+        <v>-7.6066</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.908300000000001</v>
+        <v>-8.4276</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4246</v>
+        <v>0.821</v>
       </c>
       <c r="G15" t="n">
         <v>-7.8835</v>
@@ -1624,13 +1624,13 @@
         <v>3.1154</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4967</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0656</v>
+        <v>-0.5848</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4311</v>
+        <v>-0.0347</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3863</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-21.0955</v>
+        <v>-20.8204</v>
       </c>
       <c r="E16" t="n">
-        <v>-24.4707</v>
+        <v>-24.1955</v>
       </c>
       <c r="F16" t="n">
-        <v>3.3754</v>
+        <v>3.375100000000001</v>
       </c>
       <c r="G16" t="n">
         <v>-20.4148</v>
@@ -1702,13 +1702,13 @@
         <v>18.3257</v>
       </c>
       <c r="S16" t="n">
-        <v>-3.7594</v>
+        <v>-3.4842</v>
       </c>
       <c r="T16" t="n">
-        <v>-4.5097</v>
+        <v>-4.234400000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7501</v>
+        <v>0.7503</v>
       </c>
       <c r="V16" t="n">
         <v>1.2461</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.8557</v>
+        <v>6.0558</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0009</v>
+        <v>3.424</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8548</v>
+        <v>2.6318</v>
       </c>
       <c r="G17" t="n">
         <v>5.2546</v>
@@ -1780,13 +1780,13 @@
         <v>2.1991</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5565</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8228</v>
+        <v>0.2459</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7337</v>
+        <v>0.5107</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3219</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>6.3528</v>
+        <v>5.754</v>
       </c>
       <c r="E18" t="n">
-        <v>2.9708</v>
+        <v>2.2978</v>
       </c>
       <c r="F18" t="n">
-        <v>3.3819</v>
+        <v>3.4563</v>
       </c>
       <c r="G18" t="n">
         <v>6.1132</v>
@@ -1858,13 +1858,13 @@
         <v>1.6493</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0759</v>
+        <v>0.4772</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9322</v>
+        <v>0.2591</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1438</v>
+        <v>0.2181</v>
       </c>
       <c r="V18" t="n">
         <v>2.0957</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.8402</v>
+        <v>3.0296</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2729</v>
+        <v>0.0155</v>
       </c>
       <c r="F19" t="n">
-        <v>3.1131</v>
+        <v>3.014</v>
       </c>
       <c r="G19" t="n">
         <v>1.7465</v>
@@ -1936,13 +1936,13 @@
         <v>1.8326</v>
       </c>
       <c r="S19" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.2885</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7345</v>
+        <v>-0.4461</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8336</v>
+        <v>0.7345</v>
       </c>
       <c r="V19" t="n">
         <v>1.9109</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. RAMOS SAN SEBASTIAN</t>
+          <t>H. RUEDA RIOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.7128</v>
+        <v>3.008</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2882</v>
+        <v>1.6144</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4246</v>
+        <v>1.3936</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6165</v>
+        <v>1.7889</v>
       </c>
       <c r="H20" t="n">
-        <v>0.302</v>
+        <v>1.0833</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3145</v>
+        <v>0.7056</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4444</v>
+        <v>1.6151</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6746</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="L20" t="n">
         <v>0.7698</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1721</v>
+        <v>0.1738</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3726</v>
+        <v>0.238</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5446</v>
+        <v>-0.0643</v>
       </c>
       <c r="P20" t="n">
         <v>1.0995</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0158</v>
+        <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3083</v>
+        <v>0.1195</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0717</v>
+        <v>-0.0007</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2366</v>
+        <v>0.1203</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LORENTE</t>
+          <t>R. RAMOS SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.3352</v>
+        <v>2.6662</v>
       </c>
       <c r="E21" t="n">
-        <v>0.089</v>
+        <v>0.1921</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2463</v>
+        <v>2.4741</v>
       </c>
       <c r="G21" t="n">
-        <v>4.5614</v>
+        <v>1.6165</v>
       </c>
       <c r="H21" t="n">
-        <v>3.8179</v>
+        <v>0.302</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7435</v>
+        <v>1.3145</v>
       </c>
       <c r="J21" t="n">
-        <v>4.0122</v>
+        <v>1.4444</v>
       </c>
       <c r="K21" t="n">
-        <v>3.8455</v>
+        <v>0.6746</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1667</v>
+        <v>0.7698</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5492</v>
+        <v>0.1721</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0276</v>
+        <v>-0.3726</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5768</v>
+        <v>0.5446</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.5656</v>
+        <v>1.0995</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0995</v>
+        <v>2.0158</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4007</v>
+        <v>0.2617</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6765</v>
+        <v>-0.0245</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.2862</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0613</v>
+        <v>-0.3115</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.9346</v>
+        <v>-0.3115</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. RUEDA RIOS</t>
+          <t>J. JIMENEZ LORENTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.2765</v>
+        <v>2.0438</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2298</v>
+        <v>-0.1033</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0467</v>
+        <v>2.1472</v>
       </c>
       <c r="G22" t="n">
-        <v>1.7889</v>
+        <v>4.5614</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0833</v>
+        <v>3.8179</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7056</v>
+        <v>0.7435</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6151</v>
+        <v>4.0122</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8453000000000001</v>
+        <v>3.8455</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7698</v>
+        <v>0.1667</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1738</v>
+        <v>0.5492</v>
       </c>
       <c r="N22" t="n">
-        <v>0.238</v>
+        <v>-0.0276</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0643</v>
+        <v>0.5768</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0995</v>
+        <v>-2.5656</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R22" t="n">
         <v>1.0995</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6119</v>
+        <v>1.1093</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3854</v>
+        <v>0.4842</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2266</v>
+        <v>0.6252</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.0613</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.9346</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.1267</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.6883</v>
+        <v>1.2919</v>
       </c>
       <c r="E23" t="n">
         <v>-1.2888</v>
       </c>
       <c r="F23" t="n">
-        <v>2.9771</v>
+        <v>2.5807</v>
       </c>
       <c r="G23" t="n">
         <v>2.4367</v>
@@ -2248,13 +2248,13 @@
         <v>0.9163</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6166</v>
+        <v>0.2202</v>
       </c>
       <c r="T23" t="n">
         <v>-0.405</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0215</v>
+        <v>0.6252</v>
       </c>
       <c r="V23" t="n">
         <v>-0.4486</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3085</v>
+        <v>0.8447</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.7479</v>
+        <v>-2.4594</v>
       </c>
       <c r="F25" t="n">
-        <v>3.0564</v>
+        <v>3.3041</v>
       </c>
       <c r="G25" t="n">
         <v>0.034</v>
@@ -2404,13 +2404,13 @@
         <v>2.1991</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0083</v>
+        <v>-0.4721</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9547</v>
+        <v>-0.6663</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0536</v>
+        <v>0.1942</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3613</v>
+        <v>-0.3029</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.587</v>
+        <v>-1.8755</v>
       </c>
       <c r="F26" t="n">
-        <v>1.2258</v>
+        <v>1.5726</v>
       </c>
       <c r="G26" t="n">
         <v>0.3261</v>
@@ -2482,13 +2482,13 @@
         <v>1.2828</v>
       </c>
       <c r="S26" t="n">
-        <v>0.3398</v>
+        <v>0.3982</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2911</v>
+        <v>0.0027</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0487</v>
+        <v>0.3955</v>
       </c>
       <c r="V26" t="n">
         <v>-1.3937</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.0966</v>
+        <v>-1.6654</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.5102</v>
+        <v>-3.0294</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4136</v>
+        <v>1.3641</v>
       </c>
       <c r="G27" t="n">
         <v>-2.216</v>
@@ -2560,13 +2560,13 @@
         <v>1.8326</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.1243</v>
+        <v>0.3069</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.6795</v>
+        <v>-0.1987</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5552</v>
+        <v>0.5056</v>
       </c>
       <c r="V27" t="n">
         <v>-1.5889</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.092</v>
+        <v>-2.9055</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.8224</v>
+        <v>-3.4378</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7305</v>
+        <v>0.5323</v>
       </c>
       <c r="G28" t="n">
         <v>-2.5224</v>
@@ -2638,13 +2638,13 @@
         <v>0.3665</v>
       </c>
       <c r="S28" t="n">
-        <v>0.1069</v>
+        <v>0.2934</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.3854</v>
+        <v>-0.0007</v>
       </c>
       <c r="U28" t="n">
-        <v>0.4923</v>
+        <v>0.2941</v>
       </c>
       <c r="V28" t="n">
         <v>-0.1267</v>
@@ -2671,10 +2671,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>21.09540000000001</v>
+        <v>21.0955</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.375199999999999</v>
+        <v>-3.375099999999999</v>
       </c>
       <c r="F29" t="n">
         <v>24.4708</v>
@@ -2698,7 +2698,7 @@
         <v>-2.882499999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>7.300200000000001</v>
+        <v>7.300199999999999</v>
       </c>
       <c r="N29" t="n">
         <v>1.6931</v>
@@ -2716,13 +2716,13 @@
         <v>16.4931</v>
       </c>
       <c r="S29" t="n">
-        <v>3.7593</v>
+        <v>3.7594</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.7502000000000002</v>
+        <v>-0.7501</v>
       </c>
       <c r="U29" t="n">
-        <v>4.509500000000001</v>
+        <v>4.509600000000001</v>
       </c>
       <c r="V29" t="n">
         <v>-1.246</v>
